--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:12</t>
+    <t xml:space="preserve">2026-09-09 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:06</t>
+    <t xml:space="preserve">2026-09-17 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:03</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:14</t>
+    <t xml:space="preserve">2026-10-05 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -790,7 +790,7 @@
         <v>2024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1452156.62</v>
+        <v>1452156.63</v>
       </c>
     </row>
     <row r="12">
@@ -824,7 +824,7 @@
         <v>2024</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1396161.62</v>
+        <v>1396161.63</v>
       </c>
     </row>
     <row r="14">
@@ -943,7 +943,7 @@
         <v>2024</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1306129.62</v>
+        <v>1306129.63</v>
       </c>
     </row>
     <row r="21">
@@ -960,7 +960,7 @@
         <v>2024</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1301192.62</v>
+        <v>1301192.63</v>
       </c>
     </row>
     <row r="22">
@@ -994,7 +994,7 @@
         <v>2024</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1273338.12</v>
+        <v>1273338.13</v>
       </c>
     </row>
     <row r="24">
@@ -1130,7 +1130,7 @@
         <v>2024</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1157307.12</v>
+        <v>1157307.13</v>
       </c>
     </row>
     <row r="32">
@@ -1181,7 +1181,7 @@
         <v>2024</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1094259.12</v>
+        <v>1094259.13</v>
       </c>
     </row>
     <row r="35">
@@ -1266,7 +1266,7 @@
         <v>2024</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1049473.62</v>
+        <v>1049473.63</v>
       </c>
     </row>
     <row r="40">
@@ -1334,7 +1334,7 @@
         <v>2024</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1031446.12</v>
+        <v>1031446.13</v>
       </c>
     </row>
     <row r="44">
@@ -1487,7 +1487,7 @@
         <v>2024</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>892025.62</v>
+        <v>892025.63</v>
       </c>
     </row>
     <row r="53">
